--- a/tools/importer/reports/import-newsroom-article.report.xlsx
+++ b/tools/importer/reports/import-newsroom-article.report.xlsx
@@ -88,7 +88,7 @@
     <t>newsroom-article</t>
   </si>
   <si>
-    <t>2026-07-23T15:06:38.609Z</t>
+    <t>2026-07-23T16:08:10.054Z</t>
   </si>
   <si>
     <t>How a father-and-son team from Gauteng built Essence Hair Care into a retail success story | Shoprite Holdings</t>
